--- a/data/trans_camb/IP1012-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1012-Estudios-trans_camb.xlsx
@@ -631,17 +631,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 0,0</t>
+          <t>-3,36; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 0,0</t>
+          <t>-3,01; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,91</t>
+          <t>0,0; 7,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 3,17</t>
+          <t>-0,36; 2,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 0,0</t>
+          <t>-1,82; 0,0</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,38</t>
+          <t>0,15; 1,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -797,22 +797,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,74</t>
+          <t>-1,11; 0,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,67; -0,02</t>
+          <t>-1,67; -0,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 0,76</t>
+          <t>-0,44; 0,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,86; -0,05</t>
+          <t>-0,89; -0,04</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-91,2; 242,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-68,32; 394,77</t>
+          <t>-72,17; 459,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 1,67</t>
+          <t>-1,68; 1,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 0,0</t>
+          <t>-2,38; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 1,04</t>
+          <t>-2,5; 1,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 1,75</t>
+          <t>-2,15; 1,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 0,81</t>
+          <t>-1,4; 0,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 0,6</t>
+          <t>-1,56; 0,61</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 305,25</t>
+          <t>-100,0; 313,02</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 323,68</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,85</t>
+          <t>-0,38; 0,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,81; -0,09</t>
+          <t>-0,8; -0,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 0,81</t>
+          <t>-0,75; 0,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,17</t>
+          <t>-1,17; 0,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,63</t>
+          <t>-0,37; 0,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,76; -0,03</t>
+          <t>-0,82; -0,03</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1185,22 +1185,22 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-63,84; 226,46</t>
+          <t>-68,83; 219,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-89,49; 87,44</t>
+          <t>-90,25; 50,4</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-53,15; 173,34</t>
+          <t>-52,12; 200,28</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-91,63; 24,11</t>
+          <t>-92,17; 23,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1012-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1012-Estudios-trans_camb.xlsx
@@ -631,17 +631,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 0,0</t>
+          <t>-3,6; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 0,0</t>
+          <t>-3,11; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,23</t>
+          <t>0,0; 7,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 2,81</t>
+          <t>-0,36; 3,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 0,0</t>
+          <t>-1,81; 0,0</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,69</t>
+          <t>0,15; 1,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -797,22 +797,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 0,73</t>
+          <t>-1,03; 0,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,67; -0,06</t>
+          <t>-1,57; -0,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,71</t>
+          <t>-0,42; 0,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,89; -0,04</t>
+          <t>-0,89; -0,05</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-72,17; 459,12</t>
+          <t>-69,8; 422,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 167,38</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 1,45</t>
+          <t>-1,58; 1,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 0,0</t>
+          <t>-2,55; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 1,09</t>
+          <t>-2,54; 1,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 1,54</t>
+          <t>-2,08; 1,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 0,8</t>
+          <t>-1,63; 0,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 0,61</t>
+          <t>-1,63; 0,57</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 313,02</t>
+          <t>-100,0; 292,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 323,68</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,8</t>
+          <t>-0,35; 0,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,8; -0,09</t>
+          <t>-0,83; -0,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,85</t>
+          <t>-0,78; 0,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,11</t>
+          <t>-1,09; 0,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 0,58</t>
+          <t>-0,36; 0,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,82; -0,03</t>
+          <t>-0,78; -0,02</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-100,0; 793,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1185,22 +1185,22 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-68,83; 219,9</t>
+          <t>-70,5; 171,44</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-90,25; 50,4</t>
+          <t>-88,71; 74,49</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-52,12; 200,28</t>
+          <t>-49,32; 166,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-92,17; 23,21</t>
+          <t>-92,19; 15,51</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1012-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1012-Estudios-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,17</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-0,71</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-0,71</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,17</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 0,0</t>
+          <t>0,0; 7,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,7</t>
+          <t>-3,54; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,21; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 3,11</t>
+          <t>-0,39; 3,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 0,0</t>
+          <t>-1,8; 0,0</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,18</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,65</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,52</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,18</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,65</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,4</t>
+          <t>-1,13; 0,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>-1,67; -0,02</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0,15; 1,38</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>0,0; 0,0</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-1,03; 0,7</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-1,57; -0,07</t>
-        </is>
-      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,69</t>
+          <t>-0,4; 0,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,89; -0,05</t>
+          <t>-0,86; -0,05</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-22,75%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-83,8%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-22,75%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-83,8%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-91,2; 242,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-69,8; 422,87</t>
+          <t>-68,32; 394,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 167,38</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,5</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,11</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-0,23</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>-0,79</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,5</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,11</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 1,67</t>
+          <t>-2,54; 1,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 0,0</t>
+          <t>-2,12; 1,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 1,05</t>
+          <t>-1,71; 1,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 1,52</t>
+          <t>-2,48; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 0,7</t>
+          <t>-1,49; 0,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 0,57</t>
+          <t>-1,65; 0,6</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-40,37%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-9,14%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-28,72%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-40,37%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-9,14%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 292,32</t>
+          <t>-100,0; 305,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,02</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,42</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,16</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-0,29</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,02</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,42</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,73</t>
+          <t>-0,73; 0,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,83; -0,09</t>
+          <t>-1,15; 0,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 0,75</t>
+          <t>-0,27; 0,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,14</t>
+          <t>-0,81; -0,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 0,58</t>
+          <t>-0,39; 0,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,78; -0,02</t>
+          <t>-0,76; -0,03</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-53,39%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>55,52%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-53,39%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 793,42</t>
+          <t>-63,84; 226,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-89,49; 87,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-70,5; 171,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-88,71; 74,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-49,32; 166,95</t>
+          <t>-53,15; 173,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-92,19; 15,51</t>
+          <t>-91,63; 24,11</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1012-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1012-Estudios-trans_camb.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -118,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -131,6 +134,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -497,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -591,467 +600,279 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2,17</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,71</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,71</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,68</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-0,36</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>2.171058755358308</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.7064589993198428</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-0.7064589993198428</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.6778260961492887</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-0.3612251642478284</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,91</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-3,54; 0,0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-4,21; 0,0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-0,39; 3,17</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-1,8; 0,0</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="n">
+        <v>-3.536360490452709</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-4.213054892111401</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-0.3894531993687862</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-1.796341771874101</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>187,65%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>7.909377065767753</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>3.168008452083179</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>1.876464220206562</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,18</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,65</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,52</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,14</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-0,35</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-1,13; 0,74</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-1,67; -0,02</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,15; 1,38</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,0</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-0,4; 0,76</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-0,86; -0,05</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr"/>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n"/>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-22,75%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-83,8%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>34,6%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-84,58%</t>
-        </is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>-0.1776222792821402</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.6541782874231808</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.5153859832370177</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>2.92073657964963e-06</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.1442505760991896</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-0.352622577835484</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-91,2; 242,82</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-68,32; 394,77</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-1.130878554997834</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-1.665932037543545</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.1458793836009163</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-0.4016842511763107</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-0.8578525234180914</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-0,5</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,11</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,23</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,79</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,35</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-0,42</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.7370746368117055</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>-0.02069789119878646</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1.375465743837544</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>1.680538952753931e-05</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.7588455909566327</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>-0.05448285039743128</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-2,54; 1,04</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-2,12; 1,75</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-1,71; 1,67</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-2,48; 0,0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-1,49; 0,81</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-1,65; 0,6</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>-0.2275447710866682</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-0.8380415410902993</v>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.3459923662913603</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.8457832433831359</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-40,37%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-9,14%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-28,72%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-34,99%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-41,4%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>-0.9119765650343066</v>
+      </c>
+      <c r="D14" s="6" t="inlineStr"/>
+      <c r="E14" s="6" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="n">
+        <v>-0.6832490541506547</v>
+      </c>
+      <c r="H14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 305,25</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>2.428181686166513</v>
+      </c>
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="n">
+        <v>3.947723109650854</v>
+      </c>
+      <c r="H15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1059,153 +880,289 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>0,02</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-0,42</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,16</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,29</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,09</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-0,36</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>-0.5018827668959512</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.1136641045929084</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.2255930891088441</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.7853588514495753</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-0.3510839427816022</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-0.4153394100969758</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-0,73; 0,81</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-1,15; 0,17</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-0,27; 0,85</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-0,81; -0,09</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-0,39; 0,63</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-0,76; -0,03</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-2.536240346016846</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.118367354964263</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.705486164053998</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-2.479232679540429</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-1.494523054527408</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-1.652809656765121</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-53,39%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>55,52%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>16,66%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-65,6%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.038281997112017</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1.749598974779485</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.67431678696695</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.8136736416290739</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0.5974900988057665</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>-63,84; 226,46</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>-89,49; 87,44</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>-53,15; 173,34</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-91,63; 24,11</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>-0.4036842019968164</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-0.09142454450479968</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.2872484198687719</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.3499186816308121</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.4139608825712122</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr"/>
+      <c r="D20" s="6" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr"/>
+      <c r="D21" s="6" t="inlineStr"/>
+      <c r="E21" s="6" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="n">
+        <v>3.052456062784649</v>
+      </c>
+      <c r="H21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0.02340624097149097</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.4207441836647236</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.1637783850617897</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-0.2949940568228235</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.09141055807972238</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-0.3599361488698102</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-0.7276214949517747</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-1.146219083356694</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-0.2727269142859814</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-0.8138053117618829</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-0.3906329195577001</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-0.761767254289874</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0.8133540118369084</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0.1684516704327372</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.8543253783101588</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>-0.09278978078097024</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.6321904668658526</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>-0.03421051321370884</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n"/>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>0.02970168424643062</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-0.5339093495172108</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0.5551884656553128</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.9999933612919082</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0.1665899222202371</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.6559607150869666</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>-0.638409758082206</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-0.8949477751923696</v>
+      </c>
+      <c r="E26" s="6" t="inlineStr"/>
+      <c r="F26" s="6" t="inlineStr"/>
+      <c r="G26" s="6" t="n">
+        <v>-0.5315174799224874</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.9163108956257433</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>2.264634592503322</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>0.8744365222738035</v>
+      </c>
+      <c r="E27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="inlineStr"/>
+      <c r="G27" s="6" t="n">
+        <v>1.733393231079777</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>0.241054219209829</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1213,14 +1170,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="A4:A9"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="A10:A15"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
